--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="172">
   <si>
     <t>Materia</t>
   </si>
@@ -3957,13 +3957,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -3972,22 +3972,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4001,48 +4004,57 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -4056,43 +4068,52 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>86.7</v>
       </c>
       <c r="H4">
+        <v>86.7</v>
+      </c>
+      <c r="I4">
         <v>85</v>
       </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
         <v>86.7</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>86.7</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>85</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
         <v>86.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -4106,43 +4127,52 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
         <v>96.7</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>93.3</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>90</v>
       </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
         <v>96.7</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>93.3</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>90</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
         <v>96.7</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -4156,7 +4186,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -4165,34 +4195,43 @@
         <v>100</v>
       </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
         <v>95</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
         <v>95</v>
       </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
       <c r="P6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -4206,7 +4245,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -4215,34 +4254,43 @@
         <v>100</v>
       </c>
       <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>90</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
         <v>90</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
       <c r="P7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -4256,43 +4304,52 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>93.3</v>
       </c>
       <c r="H8">
+        <v>93.3</v>
+      </c>
+      <c r="I8">
         <v>95</v>
       </c>
-      <c r="I8">
-        <v>100</v>
-      </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
         <v>93.3</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>93.3</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>95</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
         <v>93.3</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4306,7 +4363,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4315,34 +4372,43 @@
         <v>100</v>
       </c>
       <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
         <v>95</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>95</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -4356,16 +4422,16 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>93.3</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4374,25 +4440,34 @@
         <v>100</v>
       </c>
       <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10">
         <v>93.3</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>93.3</v>
       </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
         <v>93.3</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4406,43 +4481,52 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>93.3</v>
       </c>
       <c r="H11">
+        <v>93.3</v>
+      </c>
+      <c r="I11">
         <v>85</v>
       </c>
-      <c r="I11">
-        <v>100</v>
-      </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
         <v>93.3</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>93.3</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>85</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
         <v>93.3</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -4456,7 +4540,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -4474,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4491,8 +4575,17 @@
       <c r="P12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -4506,7 +4599,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -4515,34 +4608,43 @@
         <v>100</v>
       </c>
       <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
         <v>95</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>95</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4556,43 +4658,52 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>93.3</v>
       </c>
       <c r="H14">
+        <v>93.3</v>
+      </c>
+      <c r="I14">
         <v>90</v>
       </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
         <v>93.3</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>93.3</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>90</v>
       </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
         <v>93.3</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4606,43 +4717,52 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>93.3</v>
       </c>
       <c r="H15">
+        <v>93.3</v>
+      </c>
+      <c r="I15">
         <v>95</v>
       </c>
-      <c r="I15">
-        <v>100</v>
-      </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
         <v>93.3</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>93.3</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>95</v>
       </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
       <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
         <v>93.3</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4656,7 +4776,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4665,34 +4785,43 @@
         <v>100</v>
       </c>
       <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
         <v>95</v>
       </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>95</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4706,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -4715,34 +4844,43 @@
         <v>100</v>
       </c>
       <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
         <v>95</v>
       </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
         <v>95</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
       <c r="P17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4756,7 +4894,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4765,34 +4903,43 @@
         <v>100</v>
       </c>
       <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
         <v>95</v>
       </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
         <v>95</v>
       </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4806,16 +4953,16 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>93.3</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4824,25 +4971,34 @@
         <v>100</v>
       </c>
       <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
         <v>93.3</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>93.3</v>
       </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>93.3</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4856,7 +5012,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -4874,7 +5030,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4891,8 +5047,17 @@
       <c r="P20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4906,7 +5071,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4915,34 +5080,43 @@
         <v>100</v>
       </c>
       <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
         <v>95</v>
       </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
         <v>95</v>
       </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
       <c r="P21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -4956,7 +5130,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -4965,34 +5139,43 @@
         <v>100</v>
       </c>
       <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
         <v>95</v>
       </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
         <v>95</v>
       </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
       <c r="P22">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -5006,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -5015,34 +5198,43 @@
         <v>100</v>
       </c>
       <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
         <v>95</v>
       </c>
-      <c r="I23">
-        <v>100</v>
-      </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
         <v>95</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
       <c r="P23">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -5056,7 +5248,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -5065,34 +5257,43 @@
         <v>100</v>
       </c>
       <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
         <v>95</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
+        <v>100</v>
+      </c>
+      <c r="O24">
         <v>95</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
       <c r="P24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -5106,7 +5307,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -5115,34 +5316,43 @@
         <v>100</v>
       </c>
       <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
         <v>95</v>
       </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <v>100</v>
+      </c>
+      <c r="O25">
         <v>95</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
       <c r="P25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -5156,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -5165,34 +5375,43 @@
         <v>100</v>
       </c>
       <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
         <v>95</v>
       </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>95</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
       <c r="P26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -5206,7 +5425,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -5224,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5241,8 +5460,17 @@
       <c r="P27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -5256,7 +5484,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -5265,34 +5493,43 @@
         <v>100</v>
       </c>
       <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
         <v>95</v>
       </c>
-      <c r="I28">
-        <v>100</v>
-      </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
+        <v>100</v>
+      </c>
+      <c r="O28">
         <v>95</v>
       </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28">
-        <v>100</v>
-      </c>
       <c r="P28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -5306,7 +5543,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -5324,7 +5561,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5341,8 +5578,17 @@
       <c r="P29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -5356,7 +5602,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -5374,7 +5620,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5391,8 +5637,17 @@
       <c r="P30">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -5406,7 +5661,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -5415,34 +5670,43 @@
         <v>100</v>
       </c>
       <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
         <v>95</v>
       </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>95</v>
       </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
       <c r="P31">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -5456,43 +5720,52 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
         <v>93.3</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>95</v>
       </c>
-      <c r="I32">
-        <v>100</v>
-      </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
         <v>93.3</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>95</v>
       </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
       <c r="P32">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -5506,7 +5779,7 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5524,7 +5797,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5541,8 +5814,17 @@
       <c r="P33">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -5556,7 +5838,7 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -5565,34 +5847,43 @@
         <v>100</v>
       </c>
       <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
         <v>95</v>
       </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
+        <v>100</v>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
         <v>95</v>
       </c>
-      <c r="N34">
-        <v>100</v>
-      </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
       <c r="P34">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -5606,7 +5897,7 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5624,7 +5915,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5641,8 +5932,17 @@
       <c r="P35">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>100</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -5656,7 +5956,7 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -5674,7 +5974,7 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -5691,8 +5991,17 @@
       <c r="P36">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -5706,43 +6015,52 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>86.7</v>
       </c>
       <c r="H37">
+        <v>86.7</v>
+      </c>
+      <c r="I37">
         <v>95</v>
       </c>
-      <c r="I37">
-        <v>100</v>
-      </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>100</v>
+      </c>
+      <c r="M37">
         <v>86.7</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>86.7</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>95</v>
       </c>
-      <c r="N37">
-        <v>100</v>
-      </c>
-      <c r="O37">
-        <v>100</v>
-      </c>
       <c r="P37">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>100</v>
+      </c>
+      <c r="S37">
         <v>86.7</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -5756,43 +6074,52 @@
         <v>100</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>86.7</v>
       </c>
       <c r="H38">
+        <v>86.7</v>
+      </c>
+      <c r="I38">
         <v>95</v>
       </c>
-      <c r="I38">
-        <v>100</v>
-      </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>100</v>
+      </c>
+      <c r="M38">
         <v>86.7</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>86.7</v>
       </c>
-      <c r="M38">
+      <c r="O38">
         <v>95</v>
       </c>
-      <c r="N38">
-        <v>100</v>
-      </c>
-      <c r="O38">
-        <v>100</v>
-      </c>
       <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>100</v>
+      </c>
+      <c r="S38">
         <v>86.7</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:19">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -5806,7 +6133,7 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>100</v>
@@ -5815,34 +6142,43 @@
         <v>100</v>
       </c>
       <c r="H39">
+        <v>100</v>
+      </c>
+      <c r="I39">
         <v>95</v>
       </c>
-      <c r="I39">
-        <v>100</v>
-      </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <v>100</v>
       </c>
       <c r="M39">
+        <v>100</v>
+      </c>
+      <c r="N39">
+        <v>100</v>
+      </c>
+      <c r="O39">
         <v>95</v>
       </c>
-      <c r="N39">
-        <v>100</v>
-      </c>
-      <c r="O39">
-        <v>100</v>
-      </c>
       <c r="P39">
         <v>100</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -5856,7 +6192,7 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>100</v>
@@ -5874,7 +6210,7 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -5891,8 +6227,17 @@
       <c r="P40">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>100</v>
+      </c>
+      <c r="S40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
@@ -5906,7 +6251,7 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -5924,7 +6269,7 @@
         <v>100</v>
       </c>
       <c r="K41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>100</v>
@@ -5939,14 +6284,23 @@
         <v>100</v>
       </c>
       <c r="P41">
+        <v>100</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>100</v>
+      </c>
+      <c r="S41">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -206,12 +206,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -233,307 +233,40 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
     <t>ARGÜELLO</t>
   </si>
   <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>RUBALCAVA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>VENEGAS</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>NARANJO</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
     <t>AMECA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
     <t>ESTEFANIA</t>
   </si>
   <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>BIBIAN YANEL</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>EVELIN ALEXANDRA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>ANA PAOLA</t>
-  </si>
-  <si>
-    <t>ALYN</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MILDRED MARIANA</t>
-  </si>
-  <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGELICA NAOMI</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>BRYAN ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>BRIANDA RENEE</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
     <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +765,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>9</v>
@@ -1041,22 +774,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1080,13 +813,13 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1109,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -1118,22 +851,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1157,16 +890,16 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1186,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1195,22 +928,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1237,10 +970,10 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1263,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -1272,22 +1005,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1314,10 +1047,10 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1340,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -1349,22 +1082,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1394,10 +1127,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1417,7 +1150,7 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -1426,22 +1159,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1468,10 +1201,10 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1494,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1503,22 +1236,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1542,13 +1275,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1571,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1580,22 +1313,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1625,10 +1358,10 @@
         <v>5</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1648,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1657,22 +1390,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1702,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1725,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>9</v>
@@ -1734,22 +1467,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1776,10 +1509,10 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1802,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -1811,22 +1544,22 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1850,13 +1583,13 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1879,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -1888,22 +1621,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1930,10 +1663,10 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1956,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1965,22 +1698,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2010,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2033,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>9</v>
@@ -2042,22 +1775,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2081,13 +1814,13 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2110,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -2119,22 +1852,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2161,10 +1894,10 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2187,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2196,22 +1929,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2241,7 +1974,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2264,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2273,22 +2006,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2315,10 +2048,10 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2341,7 +2074,7 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>10</v>
@@ -2350,22 +2083,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2395,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2418,7 +2151,7 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>8</v>
@@ -2427,22 +2160,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2469,13 +2202,13 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2495,7 +2228,7 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2504,22 +2237,22 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2546,10 +2279,10 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2572,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -2581,22 +2314,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2620,13 +2353,13 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2649,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -2658,22 +2391,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2703,7 +2436,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2726,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>9</v>
@@ -2735,22 +2468,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2777,10 +2510,10 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2803,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -2812,22 +2545,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2854,10 +2587,10 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2880,7 +2613,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>9</v>
@@ -2889,22 +2622,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2931,10 +2664,10 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2957,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>8</v>
@@ -2966,22 +2699,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3011,10 +2744,10 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3034,7 +2767,7 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -3043,22 +2776,22 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3079,22 +2812,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3111,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -3120,22 +2853,22 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3162,10 +2895,10 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3188,7 +2921,7 @@
         <v>8</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3197,22 +2930,22 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3239,10 +2972,10 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3265,7 +2998,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3274,22 +3007,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3313,13 +3046,13 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3342,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -3351,22 +3084,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3396,7 +3129,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3419,7 +3152,7 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>9</v>
@@ -3428,22 +3161,22 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3467,13 +3200,13 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3496,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3505,22 +3238,22 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3541,22 +3274,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
         <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3573,7 +3306,7 @@
         <v>10</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F37">
         <v>9</v>
@@ -3582,22 +3315,22 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3618,22 +3351,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3650,7 +3383,7 @@
         <v>8</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F38">
         <v>9</v>
@@ -3659,22 +3392,22 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3698,13 +3431,13 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3727,7 +3460,7 @@
         <v>8</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>9</v>
@@ -3736,22 +3469,22 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3781,7 +3514,7 @@
         <v>8</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -3804,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -3813,22 +3546,22 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3855,10 +3588,10 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3881,7 +3614,7 @@
         <v>8</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F41">
         <v>8</v>
@@ -3890,22 +3623,22 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3926,22 +3659,22 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>9</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4068,7 +3801,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -4077,40 +3810,40 @@
         <v>86.7</v>
       </c>
       <c r="H4">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I4">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N4">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4127,7 +3860,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -4136,40 +3869,40 @@
         <v>96.7</v>
       </c>
       <c r="H5">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I5">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N5">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O5">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4186,7 +3919,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -4195,16 +3928,16 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I6">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4213,16 +3946,16 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -4245,7 +3978,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -4257,13 +3990,13 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4275,13 +4008,13 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4304,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4313,40 +4046,40 @@
         <v>93.3</v>
       </c>
       <c r="H8">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I8">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N8">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4363,7 +4096,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4372,40 +4105,40 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I9">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4422,7 +4155,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -4431,7 +4164,7 @@
         <v>93.3</v>
       </c>
       <c r="H10">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4440,16 +4173,16 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="N10">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -4458,13 +4191,13 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
         <v>100</v>
       </c>
       <c r="S10">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4481,7 +4214,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -4490,40 +4223,40 @@
         <v>93.3</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I11">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N11">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O11">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4540,7 +4273,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -4558,7 +4291,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4576,7 +4309,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4599,7 +4332,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -4608,16 +4341,16 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I13">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4626,16 +4359,16 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4658,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -4667,40 +4400,40 @@
         <v>93.3</v>
       </c>
       <c r="H14">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N14">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O14">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4717,7 +4450,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -4726,40 +4459,40 @@
         <v>93.3</v>
       </c>
       <c r="H15">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I15">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N15">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O15">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4776,7 +4509,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4788,13 +4521,13 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4806,13 +4539,13 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4835,7 +4568,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -4847,13 +4580,13 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4865,13 +4598,13 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4894,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4906,37 +4639,37 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4953,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -4962,7 +4695,7 @@
         <v>93.3</v>
       </c>
       <c r="H19">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4971,16 +4704,16 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N19">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4989,13 +4722,13 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5012,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -5030,7 +4763,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5048,7 +4781,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -5071,7 +4804,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -5083,13 +4816,13 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5101,13 +4834,13 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5130,7 +4863,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -5142,13 +4875,13 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5160,13 +4893,13 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5189,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -5201,13 +4934,13 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5219,13 +4952,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5248,7 +4981,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -5257,40 +4990,40 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I24">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O24">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="P24">
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5307,7 +5040,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -5316,16 +5049,16 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I25">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5334,16 +5067,16 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5366,7 +5099,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -5378,13 +5111,13 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5396,13 +5129,13 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -5425,7 +5158,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -5434,7 +5167,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -5443,7 +5176,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5452,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5461,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5484,7 +5217,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -5496,13 +5229,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5514,13 +5247,13 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5543,7 +5276,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -5552,7 +5285,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -5561,16 +5294,16 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -5579,13 +5312,13 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5602,7 +5335,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -5611,40 +5344,40 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5661,7 +5394,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -5673,37 +5406,37 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="P31">
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5720,7 +5453,7 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -5729,16 +5462,16 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I32">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -5747,16 +5480,16 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O32">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5779,7 +5512,7 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5788,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5797,16 +5530,16 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5815,13 +5548,13 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
         <v>100</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5838,7 +5571,7 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -5850,13 +5583,13 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5868,13 +5601,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5897,7 +5630,7 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5915,13 +5648,13 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -5933,13 +5666,13 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5956,7 +5689,7 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -5974,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -5992,7 +5725,7 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -6015,7 +5748,7 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -6024,40 +5757,40 @@
         <v>86.7</v>
       </c>
       <c r="H37">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I37">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>100</v>
       </c>
       <c r="M37">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N37">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O37">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6074,7 +5807,7 @@
         <v>100</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -6083,40 +5816,40 @@
         <v>86.7</v>
       </c>
       <c r="H38">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I38">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>100</v>
       </c>
       <c r="M38">
-        <v>86.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N38">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O38">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
         <v>100</v>
       </c>
       <c r="S38">
-        <v>86.7</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6133,7 +5866,7 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>100</v>
@@ -6142,16 +5875,16 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I39">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6160,16 +5893,16 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O39">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="P39">
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6192,7 +5925,7 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40">
         <v>100</v>
@@ -6210,7 +5943,7 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -6228,7 +5961,7 @@
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -6251,7 +5984,7 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -6260,7 +5993,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -6269,16 +6002,16 @@
         <v>100</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>100</v>
       </c>
       <c r="M41">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N41">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6287,13 +6020,13 @@
         <v>100</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41">
         <v>100</v>
       </c>
       <c r="S41">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -6350,7 +6083,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6359,27 +6092,30 @@
         <v>38</v>
       </c>
       <c r="D2">
+        <v>36</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>94.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>38</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6432,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6464,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6544,7 +6280,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6571,763 +6307,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920253</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920256</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920257</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920258</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920259</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920081</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920262</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920263</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920264</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920266</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920267</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920087</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920088</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920358</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920268</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920091</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920270</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920271</v>
-      </c>
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920272</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920273</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920274</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>155</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920361</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920275</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920362</v>
-      </c>
-      <c r="B26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920276</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920277</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" t="s">
-        <v>160</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920278</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>161</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051420149</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920279</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D31" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920280</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920106</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920284</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" t="s">
-        <v>166</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920285</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920286</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920358</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" t="s">
-        <v>169</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920287</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920288</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7335,7 +6314,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7370,19 +6349,19 @@
         <v>21330051920253</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7390,25 +6369,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920253</v>
+        <v>21330051920257</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7416,19 +6395,19 @@
         <v>21330051920081</v>
       </c>
       <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
         <v>77</v>
       </c>
-      <c r="C4" t="s">
-        <v>113</v>
-      </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7436,850 +6415,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920081</v>
+        <v>21330051920287</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920251</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920256</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920257</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920258</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920259</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920262</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920263</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920264</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920266</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920267</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920087</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920088</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920358</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920268</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" t="s">
-        <v>149</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920091</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>150</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920270</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920271</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920272</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920273</v>
-      </c>
-      <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920274</v>
-      </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920361</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920275</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920362</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" t="s">
-        <v>158</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920276</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920277</v>
-      </c>
-      <c r="B30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" t="s">
-        <v>160</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920278</v>
-      </c>
-      <c r="B31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051420149</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920279</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" t="s">
-        <v>163</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920280</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920106</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920284</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" t="s">
-        <v>166</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920285</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" t="s">
-        <v>167</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920286</v>
-      </c>
-      <c r="B38" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" t="s">
-        <v>168</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920358</v>
-      </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" t="s">
-        <v>169</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920287</v>
-      </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920288</v>
-      </c>
-      <c r="B41" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -783,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -860,7 +860,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -937,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -973,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1014,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1050,7 +1050,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1091,7 +1091,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1168,7 +1168,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1281,7 +1281,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1358,7 +1358,7 @@
         <v>5</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1399,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1553,7 +1553,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1666,7 +1666,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1784,7 +1784,7 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -1861,7 +1861,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -1897,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1938,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2092,7 +2092,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2169,7 +2169,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2246,7 +2246,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2323,7 +2323,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -2477,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2513,7 +2513,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2554,7 +2554,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2590,7 +2590,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2631,7 +2631,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2708,7 +2708,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -2785,7 +2785,7 @@
         <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -2898,7 +2898,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -2939,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3052,7 +3052,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3093,7 +3093,7 @@
         <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3129,7 +3129,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3170,7 +3170,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -3206,7 +3206,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3247,7 +3247,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>9</v>
@@ -3401,7 +3401,7 @@
         <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
         <v>9</v>
@@ -3478,7 +3478,7 @@
         <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>9</v>
@@ -3555,7 +3555,7 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
         <v>10</v>
@@ -3591,7 +3591,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3632,7 +3632,7 @@
         <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>9</v>
@@ -6136,7 +6136,7 @@
         <v>5.3</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -233,37 +233,19 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>VENEGAS</t>
   </si>
   <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
     <t>AMECA</t>
   </si>
   <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
   </si>
   <si>
     <t>EZEQUIEL</t>
@@ -839,7 +821,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -893,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1301,7 +1283,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1355,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -6083,7 +6065,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6104,7 +6086,7 @@
         <v>5.3</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6115,7 +6097,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6124,19 +6106,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6147,7 +6129,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6168,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6179,7 +6161,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6200,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6314,7 +6296,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6346,19 +6328,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920253</v>
+        <v>21330051920257</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
@@ -6369,70 +6351,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920257</v>
+        <v>21330051920287</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
         <v>76</v>
       </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920287</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -231,24 +231,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
   </si>
 </sst>
 </file>
@@ -774,22 +756,22 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -851,22 +833,22 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -875,10 +857,10 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -928,22 +910,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1005,22 +987,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1082,25 +1064,25 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1109,13 +1091,13 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1159,25 +1141,25 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1192,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1236,34 +1218,34 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1313,22 +1295,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1337,7 +1319,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1390,22 +1372,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1417,7 +1399,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1467,22 +1449,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1544,22 +1526,22 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1621,31 +1603,31 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1698,22 +1680,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1775,28 +1757,28 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1852,22 +1834,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1929,22 +1911,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -1953,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2006,22 +1988,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2083,22 +2065,22 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2160,34 +2142,34 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2237,22 +2219,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2314,22 +2296,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2391,22 +2373,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2468,22 +2450,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2545,22 +2527,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2622,22 +2604,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2649,7 +2631,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2699,28 +2681,28 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2776,22 +2758,22 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2800,7 +2782,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -2853,22 +2835,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2930,22 +2912,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3007,25 +2989,25 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3040,7 +3022,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3084,22 +3066,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3108,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3161,22 +3143,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3238,22 +3220,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3262,7 +3244,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3315,22 +3297,22 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3342,7 +3324,7 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3392,22 +3374,22 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>8</v>
@@ -3419,7 +3401,7 @@
         <v>7</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3469,22 +3451,22 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3546,22 +3528,22 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3573,7 +3555,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3623,22 +3605,22 @@
         <v>8</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -3650,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>9</v>
@@ -3810,10 +3792,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="N4">
-        <v>89.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O4">
-        <v>88.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3825,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>89.40000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3869,10 +3851,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N5">
-        <v>92.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="O5">
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3884,7 +3866,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3928,10 +3910,10 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3990,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>91.7</v>
+        <v>95</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4046,13 +4028,13 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N8">
-        <v>92.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O8">
-        <v>97.2</v>
+        <v>95</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4061,7 +4043,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>92.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4105,10 +4087,10 @@
         <v>95.5</v>
       </c>
       <c r="N9">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O9">
-        <v>97.2</v>
+        <v>95</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4120,7 +4102,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4164,10 +4146,10 @@
         <v>95.5</v>
       </c>
       <c r="N10">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4179,7 +4161,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4223,13 +4205,13 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N11">
-        <v>92.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O11">
-        <v>88.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4238,7 +4220,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4341,10 +4323,10 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O13">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4400,13 +4382,13 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N14">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O14">
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4415,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4459,10 +4441,10 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N15">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O15">
-        <v>97.2</v>
+        <v>90</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4474,7 +4456,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4521,7 +4503,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4580,7 +4562,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4639,7 +4621,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4651,7 +4633,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4695,7 +4677,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N19">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4710,7 +4692,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4816,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4875,7 +4857,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>97.2</v>
+        <v>95</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4934,7 +4916,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4990,7 +4972,7 @@
         <v>95.5</v>
       </c>
       <c r="N24">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="O24">
         <v>91.7</v>
@@ -5005,7 +4987,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5049,10 +5031,10 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O25">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5111,7 +5093,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5167,10 +5149,10 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -5229,7 +5211,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5285,10 +5267,10 @@
         <v>98.5</v>
       </c>
       <c r="N29">
-        <v>98.5</v>
+        <v>95.8</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5300,7 +5282,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>98.5</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5344,10 +5326,10 @@
         <v>95.5</v>
       </c>
       <c r="N30">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O30">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5359,7 +5341,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5406,7 +5388,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>94.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5418,7 +5400,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5462,10 +5444,10 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O32">
-        <v>97.2</v>
+        <v>93.3</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -5521,10 +5503,10 @@
         <v>98.5</v>
       </c>
       <c r="N33">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5536,7 +5518,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5583,7 +5565,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5639,7 +5621,7 @@
         <v>97</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -5654,7 +5636,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5698,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -5713,7 +5695,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5757,10 +5739,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="N37">
-        <v>89.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O37">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -5772,7 +5754,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>89.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5816,10 +5798,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N38">
-        <v>89.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O38">
-        <v>97.2</v>
+        <v>90</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -5831,7 +5813,7 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5875,10 +5857,10 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O39">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -5993,7 +5975,7 @@
         <v>97</v>
       </c>
       <c r="N41">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6008,7 +5990,7 @@
         <v>100</v>
       </c>
       <c r="S41">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6065,7 +6047,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6074,19 +6056,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6097,7 +6079,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6118,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6129,7 +6111,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6150,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6161,7 +6143,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6182,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6214,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6246,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6296,7 +6278,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6326,52 +6308,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920257</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920287</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -774,22 +774,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -851,22 +851,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1011,13 +1011,13 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1082,22 +1082,22 @@
         <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1159,22 +1159,22 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1239,13 +1239,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1313,22 +1313,22 @@
         <v>8</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1396,10 +1396,10 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1473,13 +1473,13 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1544,22 +1544,22 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1621,22 +1621,22 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1778,16 +1778,16 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1858,10 +1858,10 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1929,22 +1929,22 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2012,7 +2012,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2163,16 +2163,16 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2317,13 +2317,13 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2397,13 +2397,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2474,13 +2474,13 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2548,16 +2548,16 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2699,22 +2699,22 @@
         <v>8</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2776,22 +2776,22 @@
         <v>9</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2859,10 +2859,10 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -2936,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3007,13 +3007,13 @@
         <v>9</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3022,7 +3022,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3090,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3167,13 +3167,13 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3244,10 +3244,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3315,22 +3315,22 @@
         <v>9</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3392,22 +3392,22 @@
         <v>9</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3472,16 +3472,16 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3552,10 +3552,10 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3623,22 +3623,22 @@
         <v>9</v>
       </c>
       <c r="T41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6068,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6164,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ALCM - Estadisticos 20231.xlsx
+++ b/grupos/5ALCM - Estadisticos 20231.xlsx
@@ -774,22 +774,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -851,22 +851,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1011,13 +1011,13 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1082,22 +1082,22 @@
         <v>7</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1159,22 +1159,22 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1239,13 +1239,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1313,22 +1313,22 @@
         <v>8</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1396,10 +1396,10 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1473,13 +1473,13 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1544,22 +1544,22 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1621,22 +1621,22 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1778,16 +1778,16 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1858,10 +1858,10 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1929,22 +1929,22 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2012,7 +2012,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2163,16 +2163,16 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2317,13 +2317,13 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2397,13 +2397,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2474,13 +2474,13 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2548,16 +2548,16 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2699,22 +2699,22 @@
         <v>8</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2776,22 +2776,22 @@
         <v>9</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>10</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2859,10 +2859,10 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -2936,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3007,13 +3007,13 @@
         <v>9</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3022,7 +3022,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3090,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3167,13 +3167,13 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3244,10 +3244,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3315,22 +3315,22 @@
         <v>9</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3392,22 +3392,22 @@
         <v>9</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3472,16 +3472,16 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3552,10 +3552,10 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3623,22 +3623,22 @@
         <v>9</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6068,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6164,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
